--- a/templates/Template_3_LEO_II_Cohorts.xlsx
+++ b/templates/Template_3_LEO_II_Cohorts.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,23 +33,10 @@
     </font>
     <font>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00926B18"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001B4965"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="002D6A4F"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -60,18 +47,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="001B4965"/>
         <bgColor rgb="001B4965"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F5EE"/>
-        <bgColor rgb="00E8F5EE"/>
       </patternFill>
     </fill>
   </fills>
@@ -101,14 +76,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -474,15 +447,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -519,21 +492,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>106300</v>
+        <v>106234</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Martinez</t>
+          <t>Abromowicz</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Gavin</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Martinez, Carlos</t>
+          <t>Abromowicz, Gavin</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -549,21 +522,21 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>106415</v>
+        <v>106186</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Boardman</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Gavin</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Johnson, David</t>
+          <t>Boardman, Gavin</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -579,21 +552,21 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>106522</v>
+        <v>106357</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Christein</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Williams, James</t>
+          <t>Christein, Jack</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -603,108 +576,1001 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>106688</v>
+        <v>106281</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>De Pierro</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>Jake</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>De Pierro, Jake</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>106205</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Dolan</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Dolan, Liam</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>106197</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Gornell</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Finbar</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Gornell, Finbar</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>106271</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Hannon</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Ethan</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Hannon, Ethan</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>106245</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Hawkesworth</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>Michael</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Brown, Michael</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>LEO II</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>HOW TO USE:</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>List all students in the LEO II program, with their cohort assignment (A or B).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Student Name:</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Must EXACTLY match the name in Template 2 (Student Course Requests)</t>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Hawkesworth, Michael</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Cohort:</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Enter "A" or "B" — cohort A and B are pinned to specific LEO sections</t>
+      <c r="A10" s="2" t="n">
+        <v>106172</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Hermansen</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Gavin</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Hermansen, Gavin</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>TYPICAL SIZE:</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>About 36 students (18 per cohort)</t>
+      <c r="A11" s="2" t="n">
+        <v>106244</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Hurewitz</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Benny</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Hurewitz, Benny</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>DELETE:</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Delete the yellow example rows before uploading.</t>
+      <c r="A12" s="2" t="n">
+        <v>106275</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>LaBarbiera</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>LaBarbiera, Thomas</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>106247</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>McGorman</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Patrick</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>McGorman, Patrick</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>106309</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Narcisco</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Jonathan</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Narcisco, Jonathan</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>106282</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Niebergall</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Jaxson</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Niebergall, Jaxson</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>106296</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Petriello</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Petriello, Michael</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>106185</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Treco</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Connor</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Treco, Connor</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>106263</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Velez</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Cristian</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Velez, Cristian</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>106252</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Wells</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Griffin</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Wells, Griffin</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>106306</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Antaki</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Maxim</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Antaki, Maxim</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>106203</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Babb</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Aiden</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Babb, Aiden</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>106238</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Bonura</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Bonura, Michael</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>106303</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Clarke</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Griffin</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Clarke, Griffin</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>106227</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Clifford</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Clifford, Liam</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>106208</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Cozza</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Keith</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Cozza, Keith</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>106254</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Eilert</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Cooper</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Eilert, Cooper</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>106265</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Forcellati</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Luke</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Forcellati, Luke</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>106264</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Hanna</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Hanna, Joseph</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>106196</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Hauck</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Hauck, Thomas</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>106210</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Hrubec</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Hrubec, Thomas</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>106241</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Kosoff</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Luke</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Kosoff, Luke</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>106276</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Harrison</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Long, Harrison</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>106233</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>McLaughlin</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>McLaughlin, Joseph</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>106217</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Morales</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Xavier</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Morales, Xavier</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>106183</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Oblitas</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Damien</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Oblitas, Damien</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>106212</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Oh</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Oh, Lucas</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>106289</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Weinkauf</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Thijs</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Weinkauf, Thijs</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>LEO II</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B9:F9"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>